--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_antofagasta.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_antofagasta.xlsx
@@ -404,7 +404,7 @@
         <v>26.5629020289293</v>
       </c>
       <c r="D2">
-        <v>2.000201384330807</v>
+        <v>4.267656513574589</v>
       </c>
       <c r="E2">
         <v>15.62190019465845</v>
@@ -429,7 +429,7 @@
         <v>28.4419983065199</v>
       </c>
       <c r="D3">
-        <v>1.966694421315571</v>
+        <v>4.463340891912321</v>
       </c>
       <c r="E3">
         <v>14.85265225933202</v>
@@ -454,7 +454,7 @@
         <v>37.74617067833698</v>
       </c>
       <c r="D4">
-        <v>1.792156862745098</v>
+        <v>5.539393939393939</v>
       </c>
       <c r="E4">
         <v>11.58707865168539</v>
@@ -479,7 +479,7 @@
         <v>27.81999525053431</v>
       </c>
       <c r="D5">
-        <v>1.64717387052611</v>
+        <v>3.04043321299639</v>
       </c>
       <c r="E5">
         <v>20.46545991872922</v>
@@ -504,7 +504,7 @@
         <v>29.95548395302497</v>
       </c>
       <c r="D6">
-        <v>1.939656590243742</v>
+        <v>4.629622360053387</v>
       </c>
       <c r="E6">
         <v>14.25222533666784</v>
@@ -529,7 +529,7 @@
         <v>25.92592592592592</v>
       </c>
       <c r="D7">
-        <v>2.045454545454545</v>
+        <v>4.354838709677419</v>
       </c>
       <c r="E7">
         <v>15.4228855721393</v>
@@ -554,7 +554,7 @@
         <v>26.68240850059032</v>
       </c>
       <c r="D8">
-        <v>2.247280445741576</v>
+        <v>5.6129887342611</v>
       </c>
       <c r="E8">
         <v>12.32943867963069</v>
@@ -579,7 +579,7 @@
         <v>31.36689765131538</v>
       </c>
       <c r="D9">
-        <v>1.551717575411552</v>
+        <v>3.023173896922506</v>
       </c>
       <c r="E9">
         <v>20.11485680190931</v>
@@ -604,7 +604,7 @@
         <v>27.78119237861094</v>
       </c>
       <c r="D10">
-        <v>1.887470997679815</v>
+        <v>3.968292682926829</v>
       </c>
       <c r="E10">
         <v>16.47247890719164</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_antofagasta.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_antofagasta.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>26.5629020289293</v>
+      </c>
+      <c r="C2">
         <v>23.43206386969508</v>
-      </c>
-      <c r="C2">
-        <v>26.5629020289293</v>
       </c>
       <c r="D2">
         <v>4.267656513574589</v>
       </c>
       <c r="E2">
-        <v>15.62190019465845</v>
+        <v>17.70919568519527</v>
       </c>
       <c r="F2">
         <v>66.66890412014628</v>
       </c>
       <c r="G2">
-        <v>17.70919568519527</v>
+        <v>15.62190019465845</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.4419983065199</v>
+      </c>
+      <c r="C3">
         <v>22.4047417442845</v>
-      </c>
-      <c r="C3">
-        <v>28.4419983065199</v>
       </c>
       <c r="D3">
         <v>4.463340891912321</v>
       </c>
       <c r="E3">
-        <v>14.85265225933202</v>
+        <v>18.85489755823744</v>
       </c>
       <c r="F3">
         <v>66.29245018243053</v>
       </c>
       <c r="G3">
-        <v>18.85489755823744</v>
+        <v>14.85265225933202</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>37.74617067833698</v>
+      </c>
+      <c r="C4">
         <v>18.05251641137856</v>
-      </c>
-      <c r="C4">
-        <v>37.74617067833698</v>
       </c>
       <c r="D4">
         <v>5.539393939393939</v>
       </c>
       <c r="E4">
-        <v>11.58707865168539</v>
+        <v>24.22752808988765</v>
       </c>
       <c r="F4">
         <v>64.18539325842697</v>
       </c>
       <c r="G4">
-        <v>24.22752808988764</v>
+        <v>11.5870786516854</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.81999525053431</v>
+      </c>
+      <c r="C5">
         <v>32.89004986938969</v>
-      </c>
-      <c r="C5">
-        <v>27.81999525053431</v>
       </c>
       <c r="D5">
         <v>3.04043321299639</v>
       </c>
       <c r="E5">
-        <v>20.46545991872922</v>
+        <v>17.31067602512006</v>
       </c>
       <c r="F5">
         <v>62.22386405615073</v>
       </c>
       <c r="G5">
-        <v>17.31067602512006</v>
+        <v>20.46545991872922</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.95548395302497</v>
+      </c>
+      <c r="C6">
         <v>21.60003391698817</v>
-      </c>
-      <c r="C6">
-        <v>29.95548395302497</v>
       </c>
       <c r="D6">
         <v>4.629622360053387</v>
       </c>
       <c r="E6">
-        <v>14.25222533666784</v>
+        <v>19.76535356417529</v>
       </c>
       <c r="F6">
         <v>65.98242109915687</v>
       </c>
       <c r="G6">
-        <v>19.76535356417529</v>
+        <v>14.25222533666784</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>25.92592592592592</v>
+      </c>
+      <c r="C7">
         <v>22.96296296296296</v>
-      </c>
-      <c r="C7">
-        <v>25.92592592592592</v>
       </c>
       <c r="D7">
         <v>4.354838709677419</v>
       </c>
       <c r="E7">
-        <v>15.4228855721393</v>
+        <v>17.41293532338308</v>
       </c>
       <c r="F7">
         <v>67.16417910447761</v>
       </c>
       <c r="G7">
-        <v>17.41293532338308</v>
+        <v>15.4228855721393</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>26.68240850059032</v>
+      </c>
+      <c r="C8">
         <v>17.81582054309327</v>
-      </c>
-      <c r="C8">
-        <v>26.68240850059032</v>
       </c>
       <c r="D8">
         <v>5.6129887342611</v>
       </c>
       <c r="E8">
+        <v>18.4655609118392</v>
+      </c>
+      <c r="F8">
+        <v>69.2050004085301</v>
+      </c>
+      <c r="G8">
         <v>12.32943867963069</v>
-      </c>
-      <c r="F8">
-        <v>69.20500040853011</v>
-      </c>
-      <c r="G8">
-        <v>18.4655609118392</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.36689765131538</v>
+      </c>
+      <c r="C9">
         <v>33.07781934138713</v>
-      </c>
-      <c r="C9">
-        <v>31.36689765131538</v>
       </c>
       <c r="D9">
         <v>3.023173896922506</v>
       </c>
       <c r="E9">
-        <v>20.11485680190931</v>
+        <v>19.07443317422434</v>
       </c>
       <c r="F9">
         <v>60.81071002386635</v>
       </c>
       <c r="G9">
-        <v>19.07443317422434</v>
+        <v>20.11485680190931</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>27.78119237861094</v>
+      </c>
+      <c r="C10">
         <v>25.19975414874001</v>
-      </c>
-      <c r="C10">
-        <v>27.78119237861094</v>
       </c>
       <c r="D10">
         <v>3.968292682926829</v>
       </c>
       <c r="E10">
-        <v>16.47247890719164</v>
+        <v>18.15990357573323</v>
       </c>
       <c r="F10">
         <v>65.36761751707512</v>
       </c>
       <c r="G10">
-        <v>18.15990357573323</v>
+        <v>16.47247890719164</v>
       </c>
     </row>
   </sheetData>
